--- a/news_daily/2026-08-31.xlsx
+++ b/news_daily/2026-08-31.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BL20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -518,6 +518,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -819,6 +823,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -991,6 +1015,10 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1161,6 +1189,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1211,13 +1243,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1266,7 +1302,11 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>e732672bab264c1791e56f1942b6e14e</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>4a146db7a9cc8243231d007c</t>
@@ -1287,7 +1327,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -1331,6 +1375,18 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1381,13 +1437,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1436,7 +1496,11 @@
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>dcd2b33c7db24925b95a92a517ee062a</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>a6ac610a09ae75b549575eb6</t>
@@ -1457,7 +1521,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -1493,6 +1561,18 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1543,13 +1623,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1598,7 +1682,11 @@
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>ec5727c9dbe147909b3f3ceed2c761b3</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>f10be7647ef504dd94632c1e</t>
@@ -1619,7 +1707,11 @@
       <c r="AL6" s="3" t="inlineStr"/>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="3" t="inlineStr"/>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
@@ -1655,176 +1747,216 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UPS</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>United Parcel Service, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-08-31T21:16:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>UPS Settles Military Leave Class Action for $152,000, Plus Fees</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>'-0.116</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNZlZ0SFNQcHdJcTZpRWtEaDNBQkd0cG1DZWRyQi1SQ0k1WFJMTnpvaWxCYjllMHd4RW1jSWhuYUhEMDhBQTJVRmtMWlZ0YkRxUXJVR3p3OHJ3SldsSXVUVkYtZXUyOGJpdHNLblRxaS1WcV93emZJeDJJaUZybWpoXzBlWm9lSkE2SGl0TDF5LTNRSDVhOWhPVTZPeUxFQ3RGaGJKZDVUYnhkZlBxaHhIcUx3?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>news.bloombergtax.com</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>5379117460224242a1d6268e8dfe1695</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>abf2e7ee15d114d081e44722</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>9c17ad3511da0ee331a5bfa2</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr"/>
+      <c r="AL7" s="2" t="inlineStr"/>
+      <c r="AM7" s="2" t="inlineStr"/>
+      <c r="AN7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>'-0.116</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNZlZ0SFNQcHdJcTZpRWtEaDNBQkd0cG1DZWRyQi1SQ0k1WFJMTnpvaWxCYjllMHd4RW1jSWhuYUhEMDhBQTJVRmtMWlZ0YkRxUXJVR3p3OHJ3SldsSXVUVkYtZXUyOGJpdHNLblRxaS1WcV93emZJeDJJaUZybWpoXzBlWm9lSkE2SGl0TDF5LTNRSDVhOWhPVTZPeUxFQ3RGaGJKZDVUYnhkZlBxaHhIcUx3?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>news.bloombergtax.com</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>abf2e7ee15d114d081e44722</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>9c17ad3511da0ee331a5bfa2</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
+      <c r="AP7" s="2" t="inlineStr"/>
+      <c r="AQ7" s="2" t="inlineStr"/>
+      <c r="AR7" s="2" t="inlineStr"/>
+      <c r="AS7" s="2" t="inlineStr"/>
+      <c r="AT7" s="2" t="inlineStr"/>
+      <c r="AU7" s="2" t="inlineStr"/>
+      <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
+      <c r="AX7" s="2" t="inlineStr"/>
+      <c r="AY7" s="2" t="inlineStr"/>
+      <c r="AZ7" s="2" t="inlineStr"/>
+      <c r="BA7" s="2" t="inlineStr"/>
+      <c r="BB7" s="2" t="inlineStr">
         <is>
           <t>UPS</t>
         </is>
       </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="BC7" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
+      <c r="BD7" s="2" t="inlineStr"/>
+      <c r="BE7" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF7" s="3" t="inlineStr">
+      <c r="BF7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BG7" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1995,6 +2127,10 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2157,176 +2293,208 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Uber Technologies, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-08-31T18:44:00+08:00</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>New Settlement: Uber Eats Agrees to Pay Nearly $4.4M to Resolve Wage Violations</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.807</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1qNU8wUmxtSVBUUlVnTVhPemJsZU1yazdRYnFXUVZnQzk4YkxXYzI1SFozYV9lN0NJdTk2aUlOZXdIQS1uaUtxaWd2bVhubkw1TE1Hd2VvcEVVNVppenBBWEFvOGYxa0ZfYm4xOA?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>HRMorning</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>ff06ae9465b74928b70cb5453740c0ae</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>844ff906982abbd53adfae6e</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>33dd0cec444250a9f350ff12</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>0.807</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1qNU8wUmxtSVBUUlVnTVhPemJsZU1yazdRYnFXUVZnQzk4YkxXYzI1SFozYV9lN0NJdTk2aUlOZXdIQS1uaUtxaWd2bVhubkw1TE1Hd2VvcEVVNVppenBBWEFvOGYxa0ZfYm4xOA?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>HRMorning</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr">
-        <is>
-          <t>844ff906982abbd53adfae6e</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>33dd0cec444250a9f350ff12</t>
-        </is>
-      </c>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr">
+      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr">
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr"/>
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="BC10" s="3" t="inlineStr">
+      <c r="BC10" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="3" t="inlineStr"/>
-      <c r="BE10" s="3" t="inlineStr">
+      <c r="BD10" s="2" t="inlineStr"/>
+      <c r="BE10" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BG10" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2497,6 +2665,10 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2659,6 +2831,10 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2829,6 +3005,10 @@
       </c>
       <c r="BG13" s="2" t="inlineStr"/>
       <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr"/>
+      <c r="BL13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2999,6 +3179,10 @@
         </is>
       </c>
       <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BJ14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr"/>
+      <c r="BL14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3169,6 +3353,10 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr"/>
+      <c r="BL15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3219,13 +3407,17 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3274,7 +3466,11 @@
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr"/>
-      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>0aa8d0dc026141cc80f6c6c26ae4c7ee</t>
+        </is>
+      </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
           <t>5469650876f2cac73d5bc463</t>
@@ -3295,7 +3491,11 @@
       <c r="AL16" s="3" t="inlineStr"/>
       <c r="AM16" s="3" t="inlineStr"/>
       <c r="AN16" s="3" t="inlineStr"/>
-      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="3" t="inlineStr"/>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr"/>
@@ -3339,6 +3539,18 @@
         </is>
       </c>
       <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr"/>
+      <c r="BJ16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3509,6 +3721,10 @@
       </c>
       <c r="BG17" s="2" t="inlineStr"/>
       <c r="BH17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BJ17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr"/>
+      <c r="BL17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3679,6 +3895,10 @@
         </is>
       </c>
       <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr"/>
+      <c r="BL18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3849,6 +4069,10 @@
         </is>
       </c>
       <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr"/>
+      <c r="BL19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4019,9 +4243,13 @@
       </c>
       <c r="BG20" s="2" t="inlineStr"/>
       <c r="BH20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BJ20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr"/>
+      <c r="BL20" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH20"/>
+  <autoFilter ref="A1:BL20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4032,7 +4260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4095,6 +4323,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4398,6 +4630,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -4448,13 +4700,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -4503,7 +4759,11 @@
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>e732672bab264c1791e56f1942b6e14e</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>4a146db7a9cc8243231d007c</t>
@@ -4524,7 +4784,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -4568,6 +4832,18 @@
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -4618,13 +4894,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -4673,7 +4953,11 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>dcd2b33c7db24925b95a92a517ee062a</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>a6ac610a09ae75b549575eb6</t>
@@ -4694,7 +4978,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -4730,6 +5018,18 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -4780,13 +5080,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -4835,7 +5139,11 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>ec5727c9dbe147909b3f3ceed2c761b3</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>f10be7647ef504dd94632c1e</t>
@@ -4856,7 +5164,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -4892,6 +5204,18 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -4906,22 +5230,22 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>United Parcel Service, Inc. Common Stock</t>
+          <t>CVS Health Corporation Common Stock</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31T21:16:00+08:00</t>
+          <t>2026-08-31T15:00:00+08:00</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>UPS Settles Military Leave Class Action for $152,000, Plus Fees</t>
+          <t>FTC settlement with CVS Caremark: What PBMs Need to Know</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -4932,7 +5256,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -4942,13 +5266,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -4958,7 +5286,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>'-0.116</t>
+          <t>'-0.04</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr"/>
@@ -4972,12 +5300,12 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNZlZ0SFNQcHdJcTZpRWtEaDNBQkd0cG1DZWRyQi1SQ0k1WFJMTnpvaWxCYjllMHd4RW1jSWhuYUhEMDhBQTJVRmtMWlZ0YkRxUXJVR3p3OHJ3SldsSXVUVkYtZXUyOGJpdHNLblRxaS1WcV93emZJeDJJaUZybWpoXzBlWm9lSkE2SGl0TDF5LTNRSDVhOWhPVTZPeUxFQ3RGaGJKZDVUYnhkZlBxaHhIcUx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNeEhoRm1SWV82d2xSVG9xMlU0SkxKa1VnWC1oa3czUk1KS3hJbWhQZ3VubE1paV9ZWUh3empPcjNVZzMxUkFUMXZrUFF3RHJfVXc3MFRhM1NNM0YxRDRKcW81cHJNMTBFWG5QV1o0RC1temMtOGFaZ0RkNnRhNWN0c3BxVkFuUlZyZDlDaGxDZ1E2QzJ3eUNKVThjRUZHai1NWnFlcw?oc=5</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>news.bloombergtax.com</t>
+          <t>Lockton</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr"/>
@@ -4988,24 +5316,28 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>0aa8d0dc026141cc80f6c6c26ae4c7ee</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>abf2e7ee15d114d081e44722</t>
+          <t>5469650876f2cac73d5bc463</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>9c17ad3511da0ee331a5bfa2</t>
+          <t>8a79726503816209682d662d</t>
         </is>
       </c>
       <c r="AE5" s="3" t="inlineStr"/>
@@ -5018,7 +5350,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -5037,7 +5373,7 @@
       <c r="BA5" s="3" t="inlineStr"/>
       <c r="BB5" s="3" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="BC5" s="3" t="inlineStr">
@@ -5062,349 +5398,21 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31T18:44:00+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>New Settlement: Uber Eats Agrees to Pay Nearly $4.4M to Resolve Wage Violations</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>0.807</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1qNU8wUmxtSVBUUlVnTVhPemJsZU1yazdRYnFXUVZnQzk4YkxXYzI1SFozYV9lN0NJdTk2aUlOZXdIQS1uaUtxaWd2bVhubkw1TE1Hd2VvcEVVNVppenBBWEFvOGYxa0ZfYm4xOA?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>HRMorning</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>844ff906982abbd53adfae6e</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>33dd0cec444250a9f350ff12</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="BC6" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>FTC settlement with CVS Caremark: What PBMs Need to Know</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>'-0.04</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNeEhoRm1SWV82d2xSVG9xMlU0SkxKa1VnWC1oa3czUk1KS3hJbWhQZ3VubE1paV9ZWUh3empPcjNVZzMxUkFUMXZrUFF3RHJfVXc3MFRhM1NNM0YxRDRKcW81cHJNMTBFWG5QV1o0RC1temMtOGFaZ0RkNnRhNWN0c3BxVkFuUlZyZDlDaGxDZ1E2QzJ3eUNKVThjRUZHai1NWnFlcw?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Lockton</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>5469650876f2cac73d5bc463</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>8a79726503816209682d662d</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="BC7" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH7"/>
+  <autoFilter ref="A1:BL5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5415,7 +5423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5478,6 +5486,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5779,6 +5791,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -5951,6 +5983,10 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6121,6 +6157,10 @@
       </c>
       <c r="BG3" s="2" t="inlineStr"/>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -6291,6 +6331,10 @@
       </c>
       <c r="BG4" s="2" t="inlineStr"/>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -6461,9 +6505,13 @@
       </c>
       <c r="BG5" s="2" t="inlineStr"/>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH5"/>
+  <autoFilter ref="A1:BL5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6474,7 +6522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6537,6 +6585,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6840,9 +6892,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6853,7 +6925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6903,134 +6975,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -7040,46 +7112,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7088,12 +7194,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7103,90 +7209,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -7196,94 +7306,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7291,89 +7401,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-08-31.xlsx
+++ b/news_daily/2026-08-31.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -876,32 +876,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -950,7 +950,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>45c85fbd20f948f39edf96ce37a6dd85</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>b5b00a32b64d62f0f47f7118</t>
@@ -973,7 +977,7 @@
       <c r="AN2" s="2" t="inlineStr"/>
       <c r="AO2" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" s="2" t="inlineStr"/>
@@ -1015,10 +1019,22 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2866,32 +2882,32 @@
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2931,7 +2947,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2940,7 +2956,11 @@
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr"/>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>d9e5a3133f9e4d60ace50de5c8007ce6</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>52072626323863b126d8b24d</t>
@@ -2963,7 +2983,7 @@
       <c r="AN13" s="2" t="inlineStr"/>
       <c r="AO13" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP13" s="2" t="inlineStr"/>
@@ -3005,10 +3025,22 @@
       </c>
       <c r="BG13" s="2" t="inlineStr"/>
       <c r="BH13" s="2" t="inlineStr"/>
-      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ13" s="2" t="inlineStr"/>
-      <c r="BK13" s="2" t="inlineStr"/>
-      <c r="BL13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3582,32 +3614,32 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3647,7 +3679,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -3656,7 +3688,11 @@
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr"/>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>c34021fd518a4373bfb493ee4aa911ba</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>6a1de9a57b7d04070cc0795a</t>
@@ -3679,7 +3715,7 @@
       <c r="AN17" s="2" t="inlineStr"/>
       <c r="AO17" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP17" s="2" t="inlineStr"/>
@@ -3721,10 +3757,22 @@
       </c>
       <c r="BG17" s="2" t="inlineStr"/>
       <c r="BH17" s="2" t="inlineStr"/>
-      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ17" s="2" t="inlineStr"/>
-      <c r="BK17" s="2" t="inlineStr"/>
-      <c r="BL17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4104,32 +4152,32 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4169,7 +4217,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -4178,7 +4226,11 @@
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>7c9221e5f0e34970b01c6aeabe0a05d0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>d893c983aeddbea187488fbc</t>
@@ -4201,7 +4253,7 @@
       <c r="AN20" s="2" t="inlineStr"/>
       <c r="AO20" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP20" s="2" t="inlineStr"/>
@@ -4243,10 +4295,22 @@
       </c>
       <c r="BG20" s="2" t="inlineStr"/>
       <c r="BH20" s="2" t="inlineStr"/>
-      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="2" t="inlineStr"/>
-      <c r="BK20" s="2" t="inlineStr"/>
-      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL20"/>
@@ -5423,7 +5487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL5"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5814,704 +5878,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Comfort Systems USA</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31T23:07:17+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Trump’s tariff fix leaves US trade policy in permanent flux</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>關稅</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0.037</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBzbEJnSTd5RldTRGViY2tRNlZWVjVfclJoc3RXUXhya0Jva3hCb3VDNzQ0OTBHa01Scl9XOXpUQmRaTnMwejg3eE1ZS3BOaW9MX2QwdXFpNGNxMUdLQmdfamh0UWxkOWtwWC1ZSnpTTFM?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Financial Times</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>TARIFF</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>tariff</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>b5b00a32b64d62f0f47f7118</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>7304c933a6f214f09712841a</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>FIX</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>FIX</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>KeyCorp</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31T17:13:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Sarasota County shifts millions toward key hurricane evacuation route</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>'-0.033</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQajdRV0x5UTg0RUdnODNldEtGUEVrMXpsdnFSTTF6NThUWDB1ZUh5dUJweFlpY3JJUXdaeHhoWU9TbXJTb2Y3VTJNRmViU09SYkF2emZiMFp3Mm9QOC1LSE53NTVYTDA0YXBKVm51ejhseGNleFpGRG93NnNXOUpjaEd0TmVyQm1IRVplenVzSlB1d0hVZWFrN1JyUHMtWWt6LWlneXRjbktMaUlwdlhrdHpfWHNIbFNVSWdkWWlEZ0hnbUhTVTBlNG5tU091dnNxZ0Q3VUVOM2ZKQ0pfYzcxN2hhYmZwZUdsaXNJQnlENE4?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>heraldtribune.com</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>hurricane</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>52072626323863b126d8b24d</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>e94e485530b2d99fb9096274</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr"/>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>KEY</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="2" t="inlineStr">
-        <is>
-          <t>KEY</t>
-        </is>
-      </c>
-      <c r="BE3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="2" t="inlineStr"/>
-      <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
-      <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Robinhood Markets</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31T13:51:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Sunday wildfire update: Austin Fire in Mt. Hood Forest &amp; Oregon vet dies in OK wildfire</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>'-0.649</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQZlFuLUVrcDBYSldwekI0NXNIWE5aVF9YaXFpRS1fZkpRZmFPVHZ1d3ZwVEFGWU1US3BwRlBpRDVHdXAtSm16bEEyalhUVjQ4djVBUGdTRmxtWE9JTmt6VG52VDBNSExQZEw4QjVjXzM1dVBzV3N2Smg1X1lsc2l3Q3FxN24xYmRQOTlSeUlpNTgxUUg0VlZlWlpvSzVjelgxcjQtc1NTZ3FibXJNOTltNzBkM0xlQzJsWkp4c3FB?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>FOX5 Vegas</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>6a1de9a57b7d04070cc0795a</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>55c775a3bcefb8fea9e0f364</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr"/>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="BC4" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD4" s="2" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="BE4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="2" t="inlineStr"/>
-      <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
-      <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31T05:07:00+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Lowell now a category 5 hurricane, forecast to make a northward turn this weekend</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0.209</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNLXZSX245U1pxS1hBeFZCV1Q2LTdxcnNwUlRMSXl0aHlwNS1ENTVSQTVCaFc0TmV0YW5SdlVvSUNpMkttMHVWTzBWbVNWRzJKeWIyVDFDUjhPSXZLMm1XbFlwbHJIY2FlVXRRMDM3N21rbjlGM0ZMYXAyQzhDX1dEclRBRmxqRjhDcDRfbTRUSEhMaGljQUlWbHNkUmtzc1VBa0tDMVNHZGVyaXRaaHhFYlloSnBYeVk?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Hawaii News Now</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>hurricane</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>d893c983aeddbea187488fbc</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>c60eac3f97014e21e8d853b6</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr"/>
-      <c r="AM5" s="2" t="inlineStr"/>
-      <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP5" s="2" t="inlineStr"/>
-      <c r="AQ5" s="2" t="inlineStr"/>
-      <c r="AR5" s="2" t="inlineStr"/>
-      <c r="AS5" s="2" t="inlineStr"/>
-      <c r="AT5" s="2" t="inlineStr"/>
-      <c r="AU5" s="2" t="inlineStr"/>
-      <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr"/>
-      <c r="AX5" s="2" t="inlineStr"/>
-      <c r="AY5" s="2" t="inlineStr"/>
-      <c r="AZ5" s="2" t="inlineStr"/>
-      <c r="BA5" s="2" t="inlineStr"/>
-      <c r="BB5" s="2" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
-      </c>
-      <c r="BC5" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD5" s="2" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
-      </c>
-      <c r="BE5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG5" s="2" t="inlineStr"/>
-      <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
-      <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL5"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-08-31.xlsx
+++ b/news_daily/2026-08-31.xlsx
@@ -1070,28 +1070,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1131,7 +1135,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1140,7 +1144,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>056103b0af9548efa5cfef7c79228ebb</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>b41ef64e98c21f0100670351</t>
@@ -1161,7 +1169,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1205,10 +1217,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2008,28 +2032,32 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2069,7 +2097,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -2078,7 +2106,11 @@
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>3f584f580502463983671265a0a0ec0b</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>a607e99ebea65324692bc61f</t>
@@ -2099,7 +2131,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2143,10 +2179,22 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
-      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2182,28 +2230,32 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2243,7 +2295,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -2252,7 +2304,11 @@
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>5d31e1b22ad64469b9768c9c25b7f13b</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>94c068ee123f0f04f994334c</t>
@@ -2273,7 +2329,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -2309,10 +2369,22 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2546,12 +2618,12 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>分析師降評</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2561,13 +2633,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2607,7 +2683,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -2616,7 +2692,11 @@
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>3ec5c4305183469c932d9f57b822466d</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>b75f69ab8913491e551c414c</t>
@@ -2637,7 +2717,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2681,10 +2765,22 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
-      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr">
+        <is>
+          <t>Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2720,28 +2816,32 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2781,7 +2881,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -2790,7 +2890,11 @@
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>20bd5f2863b846d68847e7b0917373eb</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>ac306b797aefa5758cb2c404</t>
@@ -2811,7 +2915,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -2847,10 +2955,22 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3076,28 +3196,32 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3137,7 +3261,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -3146,7 +3270,11 @@
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr"/>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>aaa0e03f0fa5450192b1e1682d0d804a</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>30d7b0a91b52e8acdf873e4d</t>
@@ -3167,7 +3295,11 @@
       <c r="AL14" s="2" t="inlineStr"/>
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr"/>
-      <c r="AO14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="2" t="inlineStr"/>
       <c r="AQ14" s="2" t="inlineStr"/>
       <c r="AR14" s="2" t="inlineStr"/>
@@ -3211,10 +3343,22 @@
         </is>
       </c>
       <c r="BH14" s="2" t="inlineStr"/>
-      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ14" s="2" t="inlineStr"/>
-      <c r="BK14" s="2" t="inlineStr"/>
-      <c r="BL14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3250,28 +3394,32 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3311,7 +3459,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -3320,7 +3468,11 @@
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>fbeb36afbc144e3eb673cbbdd88a54f7</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>e5d7fce790e45b54492ecacc</t>
@@ -3341,7 +3493,11 @@
       <c r="AL15" s="2" t="inlineStr"/>
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="2" t="inlineStr"/>
       <c r="AQ15" s="2" t="inlineStr"/>
       <c r="AR15" s="2" t="inlineStr"/>
@@ -3385,10 +3541,22 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
-      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ15" s="2" t="inlineStr"/>
-      <c r="BK15" s="2" t="inlineStr"/>
-      <c r="BL15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3808,28 +3976,32 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3869,7 +4041,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -3878,7 +4050,11 @@
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr"/>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>8865138cba144dea93165602b40949b5</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>90489b536c3964c902c67b9c</t>
@@ -3899,7 +4075,11 @@
       <c r="AL18" s="2" t="inlineStr"/>
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr"/>
@@ -3943,10 +4123,22 @@
         </is>
       </c>
       <c r="BH18" s="2" t="inlineStr"/>
-      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ18" s="2" t="inlineStr"/>
-      <c r="BK18" s="2" t="inlineStr"/>
-      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3982,28 +4174,32 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4043,7 +4239,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -4052,7 +4248,11 @@
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr"/>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>033193afb1c74574a2f93fa742cd31e3</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>dbcc84b6826b638d56c6150d</t>
@@ -4073,7 +4273,11 @@
       <c r="AL19" s="2" t="inlineStr"/>
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="2" t="inlineStr"/>
       <c r="AQ19" s="2" t="inlineStr"/>
       <c r="AR19" s="2" t="inlineStr"/>
@@ -4117,10 +4321,22 @@
         </is>
       </c>
       <c r="BH19" s="2" t="inlineStr"/>
-      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ19" s="2" t="inlineStr"/>
-      <c r="BK19" s="2" t="inlineStr"/>
-      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
